--- a/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -303,7 +303,7 @@
     <t>EpisodeOfCare.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -663,7 +663,7 @@
     <t>EpisodeOfCare.diagnosis.condition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -710,7 +710,7 @@
     <t>EpisodeOfCare.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -729,7 +729,7 @@
     <t>EpisodeOfCare.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -764,7 +764,7 @@
     <t>EpisodeOfCare.referralRequest</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -780,7 +780,7 @@
     <t>EpisodeOfCare.careManager</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -797,7 +797,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careteam-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -810,7 +810,7 @@
     <t>EpisodeOfCare.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/account-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1135,7 +1135,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="225.77734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-episodeofcare-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>314e-constrained EpisodeOfCare profile derived from QI-Core EpisodeOfCare.
+    <t>314e-constrained EpisodeOfCare profile derived from FHIR R4 EpisodeOfCare.
 This profile applies 314e-defined extensions and uses 314e datatype profiles
 where applicable.</t>
   </si>
